--- a/request_forms/029_payment_delay_justification_application_form--request_forms.xlsx
+++ b/request_forms/029_payment_delay_justification_application_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2854,8 +2854,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'not_received_payment'}</t>
+          <t>not_received_payment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Not received payment'}</t>
+          <t>Not received payment</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'not_received_payment_confirmation'}</t>
+          <t>not_received_payment_confirmation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Not received payment confirmation'}</t>
+          <t>Not received payment confirmation</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2917,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other_reasons'}</t>
+          <t>other_reasons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other reasons'}</t>
+          <t>Other reasons</t>
         </is>
       </c>
     </row>
@@ -2934,12 +2934,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'invoice'}</t>
+          <t>invoice</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Invoice'}</t>
+          <t>Invoice</t>
         </is>
       </c>
     </row>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'receipt'}</t>
+          <t>receipt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Receipt'}</t>
+          <t>Receipt</t>
         </is>
       </c>
     </row>
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other_documents'}</t>
+          <t>other_documents</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other documents'}</t>
+          <t>Other documents</t>
         </is>
       </c>
     </row>
@@ -2985,12 +2985,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_received_payment'}</t>
+          <t>not_received_payment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not received payment'}</t>
+          <t>Not received payment</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'not_received_payment_confirmation'}</t>
+          <t>not_received_payment_confirmation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Not received payment confirmation'}</t>
+          <t>Not received payment confirmation</t>
         </is>
       </c>
     </row>
@@ -3019,12 +3019,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
